--- a/artfynd/A 28875-2024 artfynd.xlsx
+++ b/artfynd/A 28875-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118569318</v>
+        <v>118569230</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568222</v>
+        <v>568252</v>
       </c>
       <c r="R2" t="n">
-        <v>7056851</v>
+        <v>7056822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118569791</v>
+        <v>118568921</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568258</v>
+        <v>568379</v>
       </c>
       <c r="R3" t="n">
-        <v>7056679</v>
+        <v>7056668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118569901</v>
+        <v>118569318</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568273</v>
+        <v>568222</v>
       </c>
       <c r="R5" t="n">
-        <v>7056631</v>
+        <v>7056851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118568921</v>
+        <v>118569791</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568379</v>
+        <v>568258</v>
       </c>
       <c r="R6" t="n">
-        <v>7056668</v>
+        <v>7056679</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118569230</v>
+        <v>118569901</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568252</v>
+        <v>568273</v>
       </c>
       <c r="R7" t="n">
-        <v>7056822</v>
+        <v>7056631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 28875-2024 artfynd.xlsx
+++ b/artfynd/A 28875-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118568921</v>
+        <v>118570064</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568379</v>
+        <v>568439</v>
       </c>
       <c r="R3" t="n">
-        <v>7056668</v>
+        <v>7056631</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118570064</v>
+        <v>118568921</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568439</v>
+        <v>568379</v>
       </c>
       <c r="R4" t="n">
-        <v>7056631</v>
+        <v>7056668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118569318</v>
+        <v>118569791</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568222</v>
+        <v>568258</v>
       </c>
       <c r="R5" t="n">
-        <v>7056851</v>
+        <v>7056679</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118569791</v>
+        <v>118569901</v>
       </c>
       <c r="B6" t="n">
         <v>79565</v>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568258</v>
+        <v>568273</v>
       </c>
       <c r="R6" t="n">
-        <v>7056679</v>
+        <v>7056631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118569901</v>
+        <v>118569318</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568273</v>
+        <v>568222</v>
       </c>
       <c r="R7" t="n">
-        <v>7056631</v>
+        <v>7056851</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 28875-2024 artfynd.xlsx
+++ b/artfynd/A 28875-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118569230</v>
+        <v>118569791</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>79572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568252</v>
+        <v>568258</v>
       </c>
       <c r="R2" t="n">
-        <v>7056822</v>
+        <v>7056679</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118570064</v>
+        <v>118569901</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,36 +803,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568439</v>
+        <v>568273</v>
       </c>
       <c r="R3" t="n">
         <v>7056631</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118568921</v>
+        <v>118570064</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -945,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568379</v>
+        <v>568439</v>
       </c>
       <c r="R4" t="n">
-        <v>7056668</v>
+        <v>7056631</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118569791</v>
+        <v>118569318</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568258</v>
+        <v>568222</v>
       </c>
       <c r="R5" t="n">
-        <v>7056679</v>
+        <v>7056851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118569901</v>
+        <v>118569230</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568273</v>
+        <v>568252</v>
       </c>
       <c r="R6" t="n">
-        <v>7056631</v>
+        <v>7056822</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118569318</v>
+        <v>118568921</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568222</v>
+        <v>568379</v>
       </c>
       <c r="R7" t="n">
-        <v>7056851</v>
+        <v>7056668</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 28875-2024 artfynd.xlsx
+++ b/artfynd/A 28875-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118569791</v>
+        <v>118570064</v>
       </c>
       <c r="B2" t="n">
-        <v>79572</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568258</v>
+        <v>568439</v>
       </c>
       <c r="R2" t="n">
-        <v>7056679</v>
+        <v>7056631</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118570064</v>
+        <v>118569318</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568439</v>
+        <v>568222</v>
       </c>
       <c r="R4" t="n">
-        <v>7056631</v>
+        <v>7056851</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118569318</v>
+        <v>118568921</v>
       </c>
       <c r="B5" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568222</v>
+        <v>568379</v>
       </c>
       <c r="R5" t="n">
-        <v>7056851</v>
+        <v>7056668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118568921</v>
+        <v>118569791</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>79572</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kroktjärnen (Kroktjärnen), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568379</v>
+        <v>568258</v>
       </c>
       <c r="R7" t="n">
-        <v>7056668</v>
+        <v>7056679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
